--- a/TOEIC_イディオム.xlsx
+++ b/TOEIC_イディオム.xlsx
@@ -1,13 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\その他\eラーニング\TOEIC\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BECF1F42-8E76-4A42-8CC3-08376A8D25CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="イディオム" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -18,14 +24,344 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+  <si>
+    <t>英語</t>
+    <rPh sb="0" eb="2">
+      <t>エイゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日本語</t>
+    <rPh sb="0" eb="3">
+      <t>ニホンゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>kill time</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>時間をつぶす</t>
+    <rPh sb="0" eb="2">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>out of kilter</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>故障で</t>
+    <rPh sb="0" eb="2">
+      <t>コショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>不調で</t>
+    <rPh sb="0" eb="2">
+      <t>フチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>fill the bill</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目的にかなう</t>
+    <rPh sb="0" eb="2">
+      <t>モクテキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必要な標準に達する</t>
+    <rPh sb="0" eb="2">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヒョウジュン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>タッ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>work out</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>計算する</t>
+    <rPh sb="0" eb="2">
+      <t>ケイサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成就する</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウジュ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>合計で計算される</t>
+    <rPh sb="0" eb="2">
+      <t>ゴウケイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ケイサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トレーニングをする</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>計画が有効に働く</t>
+    <rPh sb="0" eb="2">
+      <t>ケイカク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ユウコウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ハタラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>結局になる</t>
+    <rPh sb="0" eb="2">
+      <t>ケッキョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>loaded down with</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>詰め込む</t>
+    <rPh sb="0" eb="1">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>get into shape</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>体をきたえる</t>
+    <rPh sb="0" eb="1">
+      <t>カラダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>体調を整える</t>
+    <rPh sb="0" eb="2">
+      <t>タイチョウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>トトノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>drop off</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>配達する</t>
+    <rPh sb="0" eb="2">
+      <t>ハイタツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>減少する</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次第にいなくなる</t>
+    <rPh sb="0" eb="2">
+      <t>シダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>眠る</t>
+    <rPh sb="0" eb="1">
+      <t>ネム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死ぬ</t>
+    <rPh sb="0" eb="1">
+      <t>シ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>on one's own</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>独力で</t>
+    <rPh sb="0" eb="2">
+      <t>ドクリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>人手を借りないで</t>
+    <rPh sb="0" eb="2">
+      <t>ヒトデ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分の責任で</t>
+    <rPh sb="0" eb="2">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>セキニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>check out</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>念入りに調べる</t>
+    <rPh sb="0" eb="2">
+      <t>ネンイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>シラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>受け取る</t>
+    <rPh sb="0" eb="1">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ホテルを出る</t>
+    <rPh sb="4" eb="5">
+      <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>退社する</t>
+    <rPh sb="0" eb="2">
+      <t>タイシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>借り出す</t>
+    <rPh sb="0" eb="1">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>crank out</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次々と排出する</t>
+    <rPh sb="0" eb="2">
+      <t>ツギツギ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハイシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>give a quick once-over</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ざっと目を通す</t>
+    <rPh sb="3" eb="4">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>トオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>wait on</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仕える</t>
+    <rPh sb="0" eb="1">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>給仕する</t>
+    <rPh sb="0" eb="2">
+      <t>キュウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -53,7 +389,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +666,183 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:H14"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="2" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.08203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.08203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/TOEIC_イディオム.xlsx
+++ b/TOEIC_イディオム.xlsx
@@ -8,24 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\その他\eラーニング\TOEIC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BECF1F42-8E76-4A42-8CC3-08376A8D25CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6C93BA6-9110-48B7-B850-3850726AD9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="イディオム" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="355">
   <si>
     <t>英語</t>
     <rPh sb="0" eb="2">
@@ -341,6 +352,2053 @@
     <t>給仕する</t>
     <rPh sb="0" eb="2">
       <t>キュウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>jerry-built</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>簡単に作られた</t>
+    <rPh sb="0" eb="2">
+      <t>カンタン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>安普請の</t>
+    <rPh sb="0" eb="1">
+      <t>ヤス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>slapped-together</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雑に作られた</t>
+    <rPh sb="0" eb="1">
+      <t>ザツ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>make up</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>構成する</t>
+    <rPh sb="0" eb="2">
+      <t>コウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>集める</t>
+    <rPh sb="0" eb="1">
+      <t>アツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>でっち上げる</t>
+    <rPh sb="3" eb="4">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>take it easy</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>くつろぐ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>のんきに構える</t>
+    <rPh sb="4" eb="5">
+      <t>カマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>気にしない</t>
+    <rPh sb="0" eb="1">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>怒らない</t>
+    <rPh sb="0" eb="1">
+      <t>オコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>さようなら</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>元気で</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>take down</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>書き留める</t>
+    <rPh sb="0" eb="1">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メモを取る</t>
+    <rPh sb="3" eb="4">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>下ろす</t>
+    <rPh sb="0" eb="1">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>取り壊す</t>
+    <rPh sb="0" eb="1">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>コワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高慢の鼻をへし折る</t>
+    <rPh sb="0" eb="2">
+      <t>コウマン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>飲み込む</t>
+    <rPh sb="0" eb="1">
+      <t>ノ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>切り倒す</t>
+    <rPh sb="0" eb="1">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>タオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>get a handle on</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>手がかりをつかむ</t>
+    <rPh sb="0" eb="1">
+      <t>テ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>make one's way</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>行く</t>
+    <rPh sb="0" eb="1">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>進む</t>
+    <rPh sb="0" eb="1">
+      <t>スス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出世する</t>
+    <rPh sb="0" eb="2">
+      <t>シュッセ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pick out</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>演奏する</t>
+    <rPh sb="0" eb="2">
+      <t>エンソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>曲を聞き覚えで演奏する</t>
+    <rPh sb="0" eb="1">
+      <t>キョク</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>オボ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>エンソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>選ぶ</t>
+    <rPh sb="0" eb="1">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>掘り出す</t>
+    <rPh sb="0" eb="1">
+      <t>ホ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>見分ける</t>
+    <rPh sb="0" eb="2">
+      <t>ミワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>聞き分ける</t>
+    <rPh sb="0" eb="1">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>認める</t>
+    <rPh sb="0" eb="1">
+      <t>ミト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>飾り立てる</t>
+    <rPh sb="0" eb="1">
+      <t>カザ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>引き立てる</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>take one's sweet time</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゆっくりとやる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>shoot out</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出す</t>
+    <rPh sb="0" eb="1">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>急に突き出す</t>
+    <rPh sb="0" eb="1">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>突出する</t>
+    <rPh sb="0" eb="2">
+      <t>トッシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>武力で解決する</t>
+    <rPh sb="0" eb="2">
+      <t>ブリョク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カイケツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>at first glance</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一見して</t>
+    <rPh sb="0" eb="2">
+      <t>イッケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一目見て</t>
+    <rPh sb="0" eb="2">
+      <t>ヒトメ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>above all</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>とりわけ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なかんずく</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>all in all</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全部</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>何より大切なもの</t>
+    <rPh sb="0" eb="1">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>タイセツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>だいたい</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>概して</t>
+    <rPh sb="0" eb="1">
+      <t>ガイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>すっかり</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>be all ears</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一心に耳を傾ける</t>
+    <rPh sb="0" eb="2">
+      <t>イッシン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ミミ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カタム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>謹聴する</t>
+    <rPh sb="0" eb="2">
+      <t>キンチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>for all I know</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>私の知る限りでは</t>
+    <rPh sb="0" eb="1">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>all out</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>完全に</t>
+    <rPh sb="0" eb="2">
+      <t>カンゼン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>総力を挙げて</t>
+    <rPh sb="0" eb="2">
+      <t>ソウリョク</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全力を尽くして</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンリョク</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>most of all</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>not at all</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>まったくない</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>once and for all</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1度だけ</t>
+    <rPh sb="1" eb="2">
+      <t>ド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今度限り</t>
+    <rPh sb="0" eb="2">
+      <t>コンド</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>きっぱりと</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>when all is said and done</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最後に</t>
+    <rPh sb="0" eb="2">
+      <t>サイゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>as a general rule</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一般的に</t>
+    <rPh sb="0" eb="3">
+      <t>イッパンテキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ほとんどの場合</t>
+    <rPh sb="5" eb="7">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>as a matter of fact</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実のところ</t>
+    <rPh sb="0" eb="1">
+      <t>ジツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>as far as anyone knows</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>周知の限りでは</t>
+    <rPh sb="0" eb="2">
+      <t>シュウチ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>as good as</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>同様に</t>
+    <rPh sb="0" eb="2">
+      <t>ドウヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>忠実で</t>
+    <rPh sb="0" eb="2">
+      <t>チュウジツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>意味がはっきりした</t>
+    <rPh sb="0" eb="2">
+      <t>イミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>as plain as day</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>as is</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そのままで</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現状のままで</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>as regular as clockwork</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>規則正しい</t>
+    <rPh sb="0" eb="2">
+      <t>キソク</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>タダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>so far as to say</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ついての真実の限りでは</t>
+    <rPh sb="4" eb="6">
+      <t>シンジツ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>just as soon as happen</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>するとすぐに</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>as it is</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>しかし実情は</t>
+    <rPh sb="3" eb="5">
+      <t>ジツジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実際は</t>
+    <rPh sb="0" eb="2">
+      <t>ジッサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>as things are</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今の成り行きでは</t>
+    <rPh sb="0" eb="1">
+      <t>イマ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ユ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現状では</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>as of</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現在での</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンザイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>as to</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ついて</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>関して</t>
+    <rPh sb="0" eb="1">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>but then</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そうは言うものの</t>
+    <rPh sb="3" eb="4">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>だがそれでは</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>all but</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>除いてすべて</t>
+    <rPh sb="0" eb="1">
+      <t>ノゾ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ほとんど</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>anything but</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>けっしてない</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>but for</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なかったら</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>nothing but</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ただだけ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>old standby</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>十八番のもの</t>
+    <rPh sb="0" eb="3">
+      <t>ジュウハチバン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>いつものもの</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>throw on</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>急いで着る</t>
+    <rPh sb="0" eb="1">
+      <t>イソ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>猟犬に獲物を追わせる</t>
+    <rPh sb="0" eb="2">
+      <t>リョウケン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>エモノ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>in a mad rush</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>非常に急いで</t>
+    <rPh sb="0" eb="2">
+      <t>ヒジョウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>イソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>cut from the same cloth</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>同じ布から裁断された</t>
+    <rPh sb="0" eb="1">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヌノ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>as plain as the nose on face</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>きわめて明白な</t>
+    <rPh sb="4" eb="6">
+      <t>メイハク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>on the house</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>店のおごりで</t>
+    <rPh sb="0" eb="1">
+      <t>ミセ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>無料で</t>
+    <rPh sb="0" eb="2">
+      <t>ムリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>keep on such a short rope</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あまり自由にさせない</t>
+    <rPh sb="3" eb="5">
+      <t>ジユウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>worship the ground walk on</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>喜ばせたいと願う</t>
+    <rPh sb="0" eb="1">
+      <t>ヨロコ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ネガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>better half</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>伴侶</t>
+    <rPh sb="0" eb="2">
+      <t>ハンリョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>配偶者</t>
+    <rPh sb="0" eb="3">
+      <t>ハイグウシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>take care of</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>世話をする</t>
+    <rPh sb="0" eb="2">
+      <t>セワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>面倒を見る</t>
+    <rPh sb="0" eb="2">
+      <t>メンドウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>man's best friend</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>人間の最良の友</t>
+    <rPh sb="0" eb="2">
+      <t>ニンゲン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サイリョウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>トモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>the king of the hill</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最高の地位にいる人</t>
+    <rPh sb="0" eb="2">
+      <t>サイコウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>チイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ヒト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>a chip off the old block</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>親にそっくりな子</t>
+    <rPh sb="0" eb="1">
+      <t>オヤ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>like peas in a pod</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>瓜二つで</t>
+    <rPh sb="0" eb="2">
+      <t>ウリフタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そっくりで</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>little bundle of joy</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>喜びのかたまり</t>
+    <rPh sb="0" eb="1">
+      <t>ヨロコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pick up</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>よくする</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>元気づく</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>拾い上げる</t>
+    <rPh sb="0" eb="1">
+      <t>ヒロ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>偶然に手に入れる</t>
+    <rPh sb="0" eb="2">
+      <t>グウゼン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>テ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>車で迎えに行く</t>
+    <rPh sb="0" eb="1">
+      <t>クルマ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ムカ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>聞き覚える</t>
+    <rPh sb="0" eb="1">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>オボ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>悪い癖を覚える</t>
+    <rPh sb="0" eb="1">
+      <t>ワル</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>クセ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>オボ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>逮捕する</t>
+    <rPh sb="0" eb="2">
+      <t>タイホ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>take one's hat off to</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>対して脱帽する</t>
+    <rPh sb="0" eb="1">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ダツボウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敬意を表する</t>
+    <rPh sb="0" eb="2">
+      <t>ケイイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>work like a dog</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>馬車馬のように働く</t>
+    <rPh sb="0" eb="3">
+      <t>バシャウマ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ハタラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>eat like a goat</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>何でも食べる</t>
+    <rPh sb="0" eb="1">
+      <t>ナン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>live out of a suitcase</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>旅行でホテル住まいをする</t>
+    <rPh sb="0" eb="2">
+      <t>リョコウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>off and on</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>断続して</t>
+    <rPh sb="0" eb="2">
+      <t>ダンゾク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>時折</t>
+    <rPh sb="0" eb="2">
+      <t>トキオリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>不規則に</t>
+    <rPh sb="0" eb="3">
+      <t>フキソク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>no one lifts a finger</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>何ひとつしない</t>
+    <rPh sb="0" eb="1">
+      <t>ナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>わずかな労さえ惜しむ</t>
+    <rPh sb="4" eb="5">
+      <t>ロウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>have half a mind to do</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>したい気がする</t>
+    <rPh sb="3" eb="4">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>しようかなと思う</t>
+    <rPh sb="6" eb="7">
+      <t>オモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pretty low on</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>十分に持たない</t>
+    <rPh sb="0" eb="2">
+      <t>ジュウブン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>get on the brain</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>凝っている</t>
+    <rPh sb="0" eb="1">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>取りつかれている</t>
+    <rPh sb="0" eb="1">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>eat, breathe and sleep</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>どっぷり漬かる</t>
+    <rPh sb="4" eb="5">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>gas guzzler</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>燃費の悪い車</t>
+    <rPh sb="0" eb="2">
+      <t>ネンピ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ワル</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>クルマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>on one's last legs</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>だめになって</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死にかけて</t>
+    <rPh sb="0" eb="1">
+      <t>シ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>loosen one's purse strings</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>財布のひもをゆるめる</t>
+    <rPh sb="0" eb="2">
+      <t>サイフ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>散財する</t>
+    <rPh sb="0" eb="2">
+      <t>サンザイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>until Hell freezes over</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>eat one out of house and home</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>よく食べる</t>
+    <rPh sb="2" eb="3">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>財政的に困らせる</t>
+    <rPh sb="0" eb="3">
+      <t>ザイセイテキ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>コマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>財産などを食いつぶす</t>
+    <rPh sb="0" eb="2">
+      <t>ザイサン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>par for the course</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>標準の</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ふつうの</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sell like hotcakes</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>飛ぶように売れる</t>
+    <rPh sb="0" eb="1">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>put one out on the street</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>家を取り上げる</t>
+    <rPh sb="0" eb="1">
+      <t>イエ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>路上へ追い出す</t>
+    <rPh sb="0" eb="2">
+      <t>ロジョウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>have a roof over one's head</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>住む場所がある</t>
+    <rPh sb="0" eb="1">
+      <t>ス</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>バショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>off the bottle</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>酒をやめる</t>
+    <rPh sb="0" eb="1">
+      <t>サケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>tie one on</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>酔っぱらう</t>
+    <rPh sb="0" eb="1">
+      <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大酒を飲む</t>
+    <rPh sb="0" eb="2">
+      <t>オオザケ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>be into</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>熱中している</t>
+    <rPh sb="0" eb="2">
+      <t>ネッチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>haul in</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>逮捕して連行する</t>
+    <rPh sb="0" eb="2">
+      <t>タイホ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>レンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pan out</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>うまくいく</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>get one's number</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>本心を見抜く</t>
+    <rPh sb="0" eb="2">
+      <t>ホンシン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ミヌ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正体を見破る</t>
+    <rPh sb="0" eb="2">
+      <t>ショウタイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ミヤブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>have one's head in the clouds</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ぼんやりする</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空想にふける</t>
+    <rPh sb="0" eb="2">
+      <t>クウソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>behind the wheel</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>運転して</t>
+    <rPh sb="0" eb="2">
+      <t>ウンテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>操縦して</t>
+    <rPh sb="0" eb="2">
+      <t>ソウジュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>make oneself at home</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>楽にする</t>
+    <rPh sb="0" eb="1">
+      <t>ラク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>膝をくずす</t>
+    <rPh sb="0" eb="1">
+      <t>ヒザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>stake out</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>縄張りをする</t>
+    <rPh sb="0" eb="2">
+      <t>ナワバ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>予約する</t>
+    <rPh sb="0" eb="2">
+      <t>ヨヤク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sell one's soul</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魂を売る</t>
+    <rPh sb="0" eb="1">
+      <t>タマシイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>利のために廉潔を捨てる</t>
+    <rPh sb="0" eb="1">
+      <t>リ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>レンケツ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>backseat driver</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>おせっかい焼き</t>
+    <rPh sb="5" eb="6">
+      <t>ヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>人にあれこれ言う人</t>
+    <rPh sb="0" eb="1">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ヒト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>eat like a bird</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>とても少食である</t>
+    <rPh sb="3" eb="5">
+      <t>ショウショク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>少ししか食べない</t>
+    <rPh sb="0" eb="1">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>get over</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>直る</t>
+    <rPh sb="0" eb="1">
+      <t>ナオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>打ち勝つ</t>
+    <rPh sb="0" eb="1">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回復する</t>
+    <rPh sb="0" eb="2">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>get an eyeful</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>十分に見て堪能する</t>
+    <rPh sb="0" eb="2">
+      <t>ジュウブン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>タンノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目に入る</t>
+    <rPh sb="0" eb="1">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ハイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>far out</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>型破りな</t>
+    <rPh sb="0" eb="2">
+      <t>カタヤブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>極端な</t>
+    <rPh sb="0" eb="2">
+      <t>キョクタン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>深遠な</t>
+    <rPh sb="0" eb="2">
+      <t>シンエン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>lady luck is smiling</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>幸運の女神が</t>
+    <rPh sb="0" eb="2">
+      <t>コウウン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>メガミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>微笑みかける</t>
+    <rPh sb="0" eb="2">
+      <t>ホホエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>運がいい</t>
+    <rPh sb="0" eb="1">
+      <t>ウン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>on the books</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>記録されて</t>
+    <rPh sb="0" eb="2">
+      <t>キロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リストに載って</t>
+    <rPh sb="4" eb="5">
+      <t>ノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>hit the books</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>勉強する</t>
+    <rPh sb="0" eb="2">
+      <t>ベンキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sit tight</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>腰を据える</t>
+    <rPh sb="0" eb="1">
+      <t>コシ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>頑張る</t>
+    <rPh sb="0" eb="2">
+      <t>ガンバ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>make a fast buck</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あぶく銭を稼ぐ</t>
+    <rPh sb="3" eb="4">
+      <t>ゼニ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カセ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>have it in for</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵意をいだく</t>
+    <rPh sb="0" eb="2">
+      <t>テキイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仕返しをしようと考えている</t>
+    <rPh sb="0" eb="2">
+      <t>シカエ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カンガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>lie low</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>じっとして時機を待つ</t>
+    <rPh sb="5" eb="7">
+      <t>ジキ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>マ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ひれ伏す</t>
+    <rPh sb="2" eb="3">
+      <t>フ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>隠れている</t>
+    <rPh sb="0" eb="1">
+      <t>カク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>the birds have all flown the coop</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>子供たちが巣立って</t>
+    <rPh sb="0" eb="2">
+      <t>コドモ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>スダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自立して</t>
+    <rPh sb="0" eb="2">
+      <t>ジリツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>not much for</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>熱心でない</t>
+    <rPh sb="0" eb="2">
+      <t>ネッシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>be on a roll</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>うまくやる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>勝ち抜きで</t>
+    <rPh sb="0" eb="1">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヌ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bat a thousand</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>すべてにおいてうまくやる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>make mincement of</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>さんざんにやっつける</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>打ち破る</t>
+    <rPh sb="0" eb="1">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヤブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>have pegged for</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>せいぜいくらいだろうと思う</t>
+    <rPh sb="11" eb="12">
+      <t>オモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>in the shop</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>修理中で</t>
+    <rPh sb="0" eb="3">
+      <t>シュウリチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>burn up</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>give the boot</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トレードに出す</t>
+    <rPh sb="5" eb="6">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クビにする</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蹴飛ばす</t>
+    <rPh sb="0" eb="2">
+      <t>ケト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>step on it</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>急ぐ</t>
+    <rPh sb="0" eb="1">
+      <t>イソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>馬力をかける</t>
+    <rPh sb="0" eb="2">
+      <t>バリキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>the milk run</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>各駅停車</t>
+    <rPh sb="0" eb="2">
+      <t>カクエキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>テイシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>やすやすとした無事な旅行</t>
+    <rPh sb="7" eb="9">
+      <t>ブジ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>リョコウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -667,16 +2725,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:H14"/>
+  <dimension ref="B2:K121"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="20.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.08203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.1640625" customWidth="1"/>
+    <col min="3" max="3" width="24.9140625" customWidth="1"/>
+    <col min="4" max="4" width="23.4140625" customWidth="1"/>
+    <col min="5" max="5" width="20.08203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.08203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.25" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.83203125" customWidth="1"/>
+    <col min="11" max="11" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.55000000000000004">
@@ -838,6 +2899,1168 @@
       </c>
       <c r="D14" t="s">
         <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18" t="s">
+        <v>58</v>
+      </c>
+      <c r="G18" t="s">
+        <v>59</v>
+      </c>
+      <c r="H18" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" t="s">
+        <v>62</v>
+      </c>
+      <c r="D19" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" t="s">
+        <v>64</v>
+      </c>
+      <c r="F19" t="s">
+        <v>65</v>
+      </c>
+      <c r="G19" t="s">
+        <v>66</v>
+      </c>
+      <c r="H19" t="s">
+        <v>67</v>
+      </c>
+      <c r="I19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" t="s">
+        <v>78</v>
+      </c>
+      <c r="F22" t="s">
+        <v>79</v>
+      </c>
+      <c r="G22" t="s">
+        <v>80</v>
+      </c>
+      <c r="H22" t="s">
+        <v>81</v>
+      </c>
+      <c r="I22" t="s">
+        <v>82</v>
+      </c>
+      <c r="J22" t="s">
+        <v>83</v>
+      </c>
+      <c r="K22" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B24" t="s">
+        <v>87</v>
+      </c>
+      <c r="C24" t="s">
+        <v>88</v>
+      </c>
+      <c r="D24" t="s">
+        <v>89</v>
+      </c>
+      <c r="E24" t="s">
+        <v>90</v>
+      </c>
+      <c r="F24" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B25" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25" t="s">
+        <v>93</v>
+      </c>
+      <c r="D25" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B26" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" t="s">
+        <v>96</v>
+      </c>
+      <c r="D26" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B27" t="s">
+        <v>98</v>
+      </c>
+      <c r="C27" t="s">
+        <v>99</v>
+      </c>
+      <c r="D27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E27" t="s">
+        <v>101</v>
+      </c>
+      <c r="F27" t="s">
+        <v>102</v>
+      </c>
+      <c r="G27" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B28" t="s">
+        <v>104</v>
+      </c>
+      <c r="C28" t="s">
+        <v>105</v>
+      </c>
+      <c r="D28" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B29" t="s">
+        <v>107</v>
+      </c>
+      <c r="C29" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B30" t="s">
+        <v>109</v>
+      </c>
+      <c r="C30" t="s">
+        <v>110</v>
+      </c>
+      <c r="D30" t="s">
+        <v>103</v>
+      </c>
+      <c r="E30" t="s">
+        <v>111</v>
+      </c>
+      <c r="F30" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B31" t="s">
+        <v>113</v>
+      </c>
+      <c r="C31" t="s">
+        <v>97</v>
+      </c>
+      <c r="D31" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B32" t="s">
+        <v>114</v>
+      </c>
+      <c r="C32" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B33" t="s">
+        <v>116</v>
+      </c>
+      <c r="C33" t="s">
+        <v>117</v>
+      </c>
+      <c r="D33" t="s">
+        <v>118</v>
+      </c>
+      <c r="E33" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B34" t="s">
+        <v>120</v>
+      </c>
+      <c r="C34" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B35" t="s">
+        <v>122</v>
+      </c>
+      <c r="C35" t="s">
+        <v>123</v>
+      </c>
+      <c r="D35" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B36" t="s">
+        <v>125</v>
+      </c>
+      <c r="C36" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B37" t="s">
+        <v>127</v>
+      </c>
+      <c r="C37" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B38" t="s">
+        <v>129</v>
+      </c>
+      <c r="C38" t="s">
+        <v>130</v>
+      </c>
+      <c r="D38" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B39" t="s">
+        <v>133</v>
+      </c>
+      <c r="C39" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B40" t="s">
+        <v>134</v>
+      </c>
+      <c r="C40" t="s">
+        <v>135</v>
+      </c>
+      <c r="D40" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B41" t="s">
+        <v>137</v>
+      </c>
+      <c r="C41" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B42" t="s">
+        <v>139</v>
+      </c>
+      <c r="C42" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B43" t="s">
+        <v>141</v>
+      </c>
+      <c r="C43" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B44" t="s">
+        <v>143</v>
+      </c>
+      <c r="C44" t="s">
+        <v>144</v>
+      </c>
+      <c r="D44" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B45" t="s">
+        <v>146</v>
+      </c>
+      <c r="C45" t="s">
+        <v>147</v>
+      </c>
+      <c r="D45" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B46" t="s">
+        <v>149</v>
+      </c>
+      <c r="C46" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B47" t="s">
+        <v>151</v>
+      </c>
+      <c r="C47" t="s">
+        <v>152</v>
+      </c>
+      <c r="D47" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B48" t="s">
+        <v>154</v>
+      </c>
+      <c r="C48" t="s">
+        <v>155</v>
+      </c>
+      <c r="D48" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B49" t="s">
+        <v>157</v>
+      </c>
+      <c r="C49" t="s">
+        <v>158</v>
+      </c>
+      <c r="D49" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B50" t="s">
+        <v>160</v>
+      </c>
+      <c r="C50" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B51" t="s">
+        <v>162</v>
+      </c>
+      <c r="C51" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B52" t="s">
+        <v>164</v>
+      </c>
+      <c r="C52" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B53" t="s">
+        <v>166</v>
+      </c>
+      <c r="C53" t="s">
+        <v>167</v>
+      </c>
+      <c r="D53" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B54" t="s">
+        <v>169</v>
+      </c>
+      <c r="C54" t="s">
+        <v>170</v>
+      </c>
+      <c r="D54" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B55" t="s">
+        <v>172</v>
+      </c>
+      <c r="C55" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B56" t="s">
+        <v>174</v>
+      </c>
+      <c r="C56" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B57" t="s">
+        <v>176</v>
+      </c>
+      <c r="C57" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B58" t="s">
+        <v>178</v>
+      </c>
+      <c r="C58" t="s">
+        <v>179</v>
+      </c>
+      <c r="D58" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B59" t="s">
+        <v>181</v>
+      </c>
+      <c r="C59" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B60" t="s">
+        <v>183</v>
+      </c>
+      <c r="C60" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B61" t="s">
+        <v>185</v>
+      </c>
+      <c r="C61" t="s">
+        <v>186</v>
+      </c>
+      <c r="D61" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B62" t="s">
+        <v>188</v>
+      </c>
+      <c r="C62" t="s">
+        <v>189</v>
+      </c>
+      <c r="D62" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B63" t="s">
+        <v>191</v>
+      </c>
+      <c r="C63" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B64" t="s">
+        <v>193</v>
+      </c>
+      <c r="C64" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B65" t="s">
+        <v>195</v>
+      </c>
+      <c r="C65" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B66" t="s">
+        <v>197</v>
+      </c>
+      <c r="C66" t="s">
+        <v>198</v>
+      </c>
+      <c r="D66" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B67" t="s">
+        <v>200</v>
+      </c>
+      <c r="C67" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B68" t="s">
+        <v>202</v>
+      </c>
+      <c r="C68" t="s">
+        <v>203</v>
+      </c>
+      <c r="D68" t="s">
+        <v>204</v>
+      </c>
+      <c r="E68" t="s">
+        <v>205</v>
+      </c>
+      <c r="F68" t="s">
+        <v>206</v>
+      </c>
+      <c r="G68" t="s">
+        <v>207</v>
+      </c>
+      <c r="H68" t="s">
+        <v>208</v>
+      </c>
+      <c r="I68" t="s">
+        <v>209</v>
+      </c>
+      <c r="J68" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B69" t="s">
+        <v>211</v>
+      </c>
+      <c r="C69" t="s">
+        <v>212</v>
+      </c>
+      <c r="D69" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B70" t="s">
+        <v>214</v>
+      </c>
+      <c r="C70" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B71" t="s">
+        <v>216</v>
+      </c>
+      <c r="C71" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B72" t="s">
+        <v>218</v>
+      </c>
+      <c r="C72" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B73" t="s">
+        <v>220</v>
+      </c>
+      <c r="C73" t="s">
+        <v>221</v>
+      </c>
+      <c r="D73" t="s">
+        <v>222</v>
+      </c>
+      <c r="E73" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B74" t="s">
+        <v>224</v>
+      </c>
+      <c r="C74" t="s">
+        <v>225</v>
+      </c>
+      <c r="D74" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B75" t="s">
+        <v>227</v>
+      </c>
+      <c r="C75" t="s">
+        <v>228</v>
+      </c>
+      <c r="D75" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B76" t="s">
+        <v>230</v>
+      </c>
+      <c r="C76" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B77" t="s">
+        <v>232</v>
+      </c>
+      <c r="C77" t="s">
+        <v>233</v>
+      </c>
+      <c r="D77" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B78" t="s">
+        <v>235</v>
+      </c>
+      <c r="C78" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B79" t="s">
+        <v>237</v>
+      </c>
+      <c r="C79" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B80" t="s">
+        <v>239</v>
+      </c>
+      <c r="C80" t="s">
+        <v>240</v>
+      </c>
+      <c r="D80" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="81" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B81" t="s">
+        <v>242</v>
+      </c>
+      <c r="C81" t="s">
+        <v>243</v>
+      </c>
+      <c r="D81" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="82" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B82" t="s">
+        <v>245</v>
+      </c>
+      <c r="C82" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="83" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B83" t="s">
+        <v>246</v>
+      </c>
+      <c r="C83" t="s">
+        <v>247</v>
+      </c>
+      <c r="D83" t="s">
+        <v>248</v>
+      </c>
+      <c r="E83" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="84" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B84" t="s">
+        <v>250</v>
+      </c>
+      <c r="C84" t="s">
+        <v>251</v>
+      </c>
+      <c r="D84" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="85" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B85" t="s">
+        <v>253</v>
+      </c>
+      <c r="C85" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="86" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B86" t="s">
+        <v>255</v>
+      </c>
+      <c r="C86" t="s">
+        <v>256</v>
+      </c>
+      <c r="D86" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="87" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B87" t="s">
+        <v>258</v>
+      </c>
+      <c r="C87" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="88" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B88" t="s">
+        <v>260</v>
+      </c>
+      <c r="C88" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="89" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B89" t="s">
+        <v>262</v>
+      </c>
+      <c r="C89" t="s">
+        <v>263</v>
+      </c>
+      <c r="D89" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="90" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B90" t="s">
+        <v>265</v>
+      </c>
+      <c r="C90" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="91" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B91" t="s">
+        <v>267</v>
+      </c>
+      <c r="C91" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="92" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B92" t="s">
+        <v>269</v>
+      </c>
+      <c r="C92" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="93" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B93" t="s">
+        <v>271</v>
+      </c>
+      <c r="C93" t="s">
+        <v>272</v>
+      </c>
+      <c r="D93" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="94" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B94" t="s">
+        <v>274</v>
+      </c>
+      <c r="C94" t="s">
+        <v>275</v>
+      </c>
+      <c r="D94" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="95" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B95" t="s">
+        <v>277</v>
+      </c>
+      <c r="C95" t="s">
+        <v>278</v>
+      </c>
+      <c r="D95" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="96" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B96" t="s">
+        <v>280</v>
+      </c>
+      <c r="C96" t="s">
+        <v>281</v>
+      </c>
+      <c r="D96" t="s">
+        <v>55</v>
+      </c>
+      <c r="E96" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="97" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B97" t="s">
+        <v>283</v>
+      </c>
+      <c r="C97" t="s">
+        <v>284</v>
+      </c>
+      <c r="D97" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="98" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B98" t="s">
+        <v>286</v>
+      </c>
+      <c r="C98" t="s">
+        <v>287</v>
+      </c>
+      <c r="D98" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="99" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B99" t="s">
+        <v>289</v>
+      </c>
+      <c r="C99" t="s">
+        <v>290</v>
+      </c>
+      <c r="D99" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="100" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B100" t="s">
+        <v>292</v>
+      </c>
+      <c r="C100" t="s">
+        <v>293</v>
+      </c>
+      <c r="D100" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="101" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B101" t="s">
+        <v>295</v>
+      </c>
+      <c r="C101" t="s">
+        <v>296</v>
+      </c>
+      <c r="D101" t="s">
+        <v>297</v>
+      </c>
+      <c r="E101" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="102" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B102" t="s">
+        <v>299</v>
+      </c>
+      <c r="C102" t="s">
+        <v>300</v>
+      </c>
+      <c r="D102" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="103" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B103" t="s">
+        <v>302</v>
+      </c>
+      <c r="C103" t="s">
+        <v>303</v>
+      </c>
+      <c r="D103" t="s">
+        <v>304</v>
+      </c>
+      <c r="E103" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="104" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B104" t="s">
+        <v>306</v>
+      </c>
+      <c r="C104" t="s">
+        <v>307</v>
+      </c>
+      <c r="D104" t="s">
+        <v>308</v>
+      </c>
+      <c r="E104" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="105" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B105" t="s">
+        <v>310</v>
+      </c>
+      <c r="C105" t="s">
+        <v>311</v>
+      </c>
+      <c r="D105" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="106" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B106" t="s">
+        <v>313</v>
+      </c>
+      <c r="C106" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="107" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B107" t="s">
+        <v>315</v>
+      </c>
+      <c r="C107" t="s">
+        <v>316</v>
+      </c>
+      <c r="D107" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="108" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B108" t="s">
+        <v>318</v>
+      </c>
+      <c r="C108" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="109" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B109" t="s">
+        <v>320</v>
+      </c>
+      <c r="C109" t="s">
+        <v>321</v>
+      </c>
+      <c r="D109" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="110" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B110" t="s">
+        <v>323</v>
+      </c>
+      <c r="C110" t="s">
+        <v>324</v>
+      </c>
+      <c r="D110" t="s">
+        <v>325</v>
+      </c>
+      <c r="E110" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="111" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B111" t="s">
+        <v>327</v>
+      </c>
+      <c r="C111" t="s">
+        <v>328</v>
+      </c>
+      <c r="D111" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="112" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B112" t="s">
+        <v>330</v>
+      </c>
+      <c r="C112" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="113" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B113" t="s">
+        <v>332</v>
+      </c>
+      <c r="C113" t="s">
+        <v>333</v>
+      </c>
+      <c r="D113" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="114" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B114" t="s">
+        <v>335</v>
+      </c>
+      <c r="C114" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="115" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B115" t="s">
+        <v>337</v>
+      </c>
+      <c r="C115" t="s">
+        <v>338</v>
+      </c>
+      <c r="D115" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="116" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B116" t="s">
+        <v>340</v>
+      </c>
+      <c r="C116" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="117" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B117" t="s">
+        <v>342</v>
+      </c>
+      <c r="C117" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="118" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B118" t="s">
+        <v>344</v>
+      </c>
+      <c r="C118" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="119" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B119" t="s">
+        <v>345</v>
+      </c>
+      <c r="C119" t="s">
+        <v>346</v>
+      </c>
+      <c r="D119" t="s">
+        <v>347</v>
+      </c>
+      <c r="E119" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="120" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B120" t="s">
+        <v>349</v>
+      </c>
+      <c r="C120" t="s">
+        <v>350</v>
+      </c>
+      <c r="D120" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="121" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B121" t="s">
+        <v>352</v>
+      </c>
+      <c r="C121" t="s">
+        <v>353</v>
+      </c>
+      <c r="D121" t="s">
+        <v>354</v>
       </c>
     </row>
   </sheetData>
